--- a/SALT_PRICES_1410.xlsx
+++ b/SALT_PRICES_1410.xlsx
@@ -100,32 +100,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +513,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -515,635 +538,653 @@
     <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Соль: прибыль лотов при разной себестоимости (снижение на торгах 15%, чистая после УСН 15%)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="81" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Лот</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Подача</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Тонн</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Цена в НМЦК, ₽/т</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>A: ваша КЗ 2 500: маржа</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>A: ваша КЗ 2 500: прибыль, ₽</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>A: ваша КЗ 2 500: безубыток</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>B: опт тип D + доставка ≈5 000: маржа</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>B: опт тип D + доставка ≈5 000: прибыль, ₽</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>B: опт тип D + доставка ≈5 000: безубыток</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>C: 4 500 (не подтверждено): маржа</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>C: 4 500 (не подтверждено): прибыль, ₽</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>C: 4 500 (не подтверждено): безубыток</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>D: дилер МКР + доставка ≈8 000: маржа</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>D: дилер МКР + доставка ≈8 000: прибыль, ₽</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>D: дилер МКР + доставка ≈8 000: безубыток</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ДГХ, Московская обл.</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>32616451106</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>6724000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>16810</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="8" t="n">
         <v>0.851279000594884</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="9" t="n">
         <v>3941280.074520547</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="8" t="n">
         <v>0.8451507490727774</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="8" t="n">
         <v>0.702558001189768</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="K3" s="9" t="n">
         <v>3063334.869041095</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="8" t="n">
         <v>0.6903014981455549</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="8" t="n">
         <v>0.7323022010707912</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="N3" s="9" t="n">
         <v>3238923.910136987</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="O3" s="8" t="n">
         <v>0.7212713483309994</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="P3" s="8" t="n">
         <v>0.5240928019036288</v>
       </c>
-      <c r="Q3" s="7" t="n">
+      <c r="Q3" s="9" t="n">
         <v>2009800.622465753</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="8" t="n">
         <v>0.5044823970328879</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Новосибирск</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>0851300006226000106</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>4400000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="8" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="9" t="n">
         <v>2275622.794520548</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>0.7633621901739445</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="9" t="n">
         <v>1397677.589041096</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="8" t="n">
         <v>0.5267243803478889</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="8" t="n">
         <v>0.5909090909090909</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="9" t="n">
         <v>1573266.630136986</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="8" t="n">
         <v>0.5740519423131</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="Q4" s="7" t="n">
+      <c r="Q4" s="9" t="n">
         <v>344143.3424657534</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="8" t="n">
         <v>0.2427590085566223</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Волоколамск, МО</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>32616447519</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1593800</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>12260</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="8" t="n">
         <v>0.7960848287112561</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="9" t="n">
         <v>856976.144219178</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="8" t="n">
         <v>0.7876822260940773</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="8" t="n">
         <v>0.5921696574225123</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="9" t="n">
         <v>571643.9524383562</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="8" t="n">
         <v>0.5753644521881548</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="8" t="n">
         <v>0.632952691680261</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="9" t="n">
         <v>628710.3907945206</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="8" t="n">
         <v>0.6178280069693394</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="8" t="n">
         <v>0.3474714518760196</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="10" t="n">
         <v>229245.3223013698</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="8" t="n">
         <v>0.3205831235010478</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Абинск, Краснодарский край</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>0318300065126000256</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>1368000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>9120</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.7258771929824561</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="9" t="n">
         <v>651243.5079452054</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>0.7145815890255909</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="8" t="n">
         <v>0.4517543859649123</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="9" t="n">
         <v>322014.055890411</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="8" t="n">
         <v>0.4291631780511819</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="8" t="n">
         <v>0.506578947368421</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="N6" s="9" t="n">
         <v>387859.9463013698</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="8" t="n">
         <v>0.4862468602460637</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.1228070175438596</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="11" t="n">
         <v>-85954.45479452054</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="8" t="n">
         <v>0.086661084881891</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Воронеж</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>0131300000626001316</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>3296150</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="7" t="n">
         <v>461</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>7150</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="8" t="n">
         <v>0.6503496503496503</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="9" t="n">
         <v>1350584.778684932</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="8" t="n">
         <v>0.6359418310368377</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="8" t="n">
         <v>0.3006993006993007</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="9" t="n">
         <v>338752.929369863</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="8" t="n">
         <v>0.2718836620736754</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" s="8" t="n">
         <v>0.3706293706293706</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="N7" s="9" t="n">
         <v>541119.2992328767</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="O7" s="8" t="n">
         <v>0.3446952958663077</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="8" t="n">
         <v>-0.1188811188811189</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="11" t="n">
         <v>-1029935.635068493</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" s="8" t="n">
         <v>-0.1649861406821195</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Струнино, Владимирская обл.</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>0128600006826000407</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>1342500</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>8950</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="8" t="n">
         <v>0.7206703910614525</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="9" t="n">
         <v>632967.1479452054</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>0.7091602337333396</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="8" t="n">
         <v>0.441340782122905</v>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="K8" s="9" t="n">
         <v>303737.695890411</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="8" t="n">
         <v>0.4183204674666792</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="M8" s="8" t="n">
         <v>0.4972067039106145</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="N8" s="9" t="n">
         <v>369583.5863013699</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="O8" s="8" t="n">
         <v>0.4764884207200112</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.106145251396648</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="11" t="n">
         <v>-107456.0547945205</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="8" t="n">
         <v>0.06931274794668668</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Школа № 525, СПб (мешки 20–25 кг)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>0372200193426000027</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>16.10</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>106470</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="7" t="n">
         <v>6.5</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>16380</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="8" t="n">
         <v>0.8473748473748474</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="10" t="n">
         <v>62042.56881095891</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="8" t="n">
         <v>0.8410857198970323</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="8" t="n">
         <v>0.6947496947496947</v>
       </c>
-      <c r="K9" s="8" t="n">
+      <c r="K9" s="10" t="n">
         <v>47775.95922191781</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="8" t="n">
         <v>0.6821714397940646</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="M9" s="8" t="n">
         <v>0.7252747252747253</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="10" t="n">
         <v>50629.28113972603</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="O9" s="8" t="n">
         <v>0.7139542958146581</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="8" t="n">
         <v>0.5115995115995116</v>
       </c>
-      <c r="Q9" s="8" t="n">
+      <c r="Q9" s="10" t="n">
         <v>30656.0277150685</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R9" s="8" t="n">
         <v>0.4914743036705034</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Самара (нужен опыт 24,2 млн)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>0142200001326018965</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>121000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="7" t="n">
         <v>11000</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="9" t="n">
         <v>62579626.84931506</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="8" t="n">
         <v>0.7633621901739445</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="8" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="9" t="n">
         <v>38436133.69863014</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="8" t="n">
         <v>0.5267243803478889</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="M10" s="8" t="n">
         <v>0.5909090909090909</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="N10" s="9" t="n">
         <v>43264832.32876713</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="O10" s="8" t="n">
         <v>0.5740519423131001</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="Q10" s="9" t="n">
         <v>9463941.91780822</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="8" t="n">
         <v>0.2427590085566223</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ИТОГО без Самары</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="11" t="n">
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="12" t="inlineStr"/>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="12" t="inlineStr"/>
+      <c r="H11" s="13" t="n">
         <v>9770717.016646573</v>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="11" t="n">
+      <c r="I11" s="12" t="inlineStr"/>
+      <c r="J11" s="12" t="inlineStr"/>
+      <c r="K11" s="13" t="n">
         <v>6044937.050893151</v>
       </c>
-      <c r="L11" s="10" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="11" t="n">
+      <c r="L11" s="12" t="inlineStr"/>
+      <c r="M11" s="12" t="inlineStr"/>
+      <c r="N11" s="13" t="n">
         <v>6790093.044043835</v>
       </c>
-      <c r="O11" s="10" t="inlineStr"/>
-      <c r="P11" s="10" t="inlineStr"/>
-      <c r="Q11" s="11" t="n">
+      <c r="O11" s="12" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="13" t="n">
         <v>1390499.170290411</v>
       </c>
-      <c r="R11" s="10" t="inlineStr"/>
+      <c r="R11" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1151,7 +1192,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1164,693 +1205,693 @@
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Производитель</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Продукт / фасовка</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Цена от, ₽/т</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Условия</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>esolk.ru (ЕСК)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Павлодарсоль / Аралтуз (Казахстан), Уралкалий, Белкалий, Тыреть, АСК</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Галит тип B/C, помол 2–3, навалом</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="15" t="n">
         <v>1990</v>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>без НДС, без доставки, от вагона (~70 т), станция отгрузки</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>https://www.esolk.ru/produktsiya/kontsentrat-mineralnyy-galit/mkr-1-tonna/</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Ваша цена</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Казахстан</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>МКР, НДС вкл., с доставкой в РФ</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>данные клиента — проверить, куда именно доставка</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru (Люберцы)</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Тип D, от 40 т, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>4350</v>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>самовывоз, НДС не указан</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Тип D, до 40 т, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>4550</v>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>тендер Алтайский край (saby.ru)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>НМЦК 2 430 т = 13,37 млн</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>5500</v>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>начальная цена заказчика, ориентир</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>https://saby.ru/tenders/card/245190387</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Илецкая (Руссоль)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Тип C, россыпь</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>5750</v>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Тип C, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Уралкалий / Белкалий</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Тип A с антислеживателем, биг-бэг</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/tip-a/uralkaliy-big-beg-s-antislezhivatelem</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru (Москва)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Астрахань</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Аралтуз / Индертуз / Алтайсоль (КЗ)</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>7000</v>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>perevalka24.ru</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Уралкалий «Галит» марка А</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>биг-бэг 1000 кг</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>7000</v>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>https://perevalka24.ru/product/peskosol/kontsentrat-mineralnyy-galit-marki-a-big-beg-1000kg-1-tonna/</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru (Москва)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>навалом</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>7300</v>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>самовывоз; доставка 8–11 тыс. за машину 20–25 м³ до 60 км</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>https://perevalka-tsk.ru/product/pg-materialy/tekhnicheskaya-sol/tekhnicheskaya-sol-araltuz/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Беларуськалий / Баскунчак</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru (Москва)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь, от 2 т</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>7800</v>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>8000</v>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>навалом / биг-бэг</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>8700</v>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>https://perevalka-tsk.ru/product/pg-materialy/tekhnicheskaya-sol/tekhnicheskaya-sol-araltuz/</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>opt6.ru</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>МКР, помол 2 тип Б</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>9990</v>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>https://opt6.ru/products/tekhnicheskaya_sol_mkr/</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Тыреть / Илецксоль</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Илецкая</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Руссоль-центр</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Руссоль</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>мешки/МКР, от 10 т</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="15" t="n">
         <v>11300</v>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>опт, по данным выдачи поиска (сайт 403)</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>https://www.xn----jtbqkblfcapd5b2e.xn--p1ai/catalog/k-6070503-sol_tekhnicheskaya</t>
         </is>
@@ -1882,5 +1923,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>